--- a/anime_library/anime_data.xlsx
+++ b/anime_library/anime_data.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="50">
   <si>
     <t>№</t>
   </si>
@@ -131,15 +131,47 @@
   </si>
   <si>
     <t>орендар</t>
+  </si>
+  <si>
+    <t>Твоє ім'я</t>
+  </si>
+  <si>
+    <t>Міцуха</t>
+  </si>
+  <si>
+    <t>Такі</t>
+  </si>
+  <si>
+    <t>Мікі</t>
+  </si>
+  <si>
+    <t>Цукаса</t>
+  </si>
+  <si>
+    <t>Йоцуха</t>
+  </si>
+  <si>
+    <t>Саяка</t>
+  </si>
+  <si>
+    <t>Шінта</t>
+  </si>
+  <si>
+    <t>Тосікі</t>
+  </si>
+  <si>
+    <t>Юкарі</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="d.m.yyyy"/>
     <numFmt numFmtId="165" formatCode="dd.mm.yyyy"/>
+    <numFmt numFmtId="166" formatCode="dd.mm"/>
+    <numFmt numFmtId="167" formatCode="d.m"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -195,7 +227,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -218,6 +250,12 @@
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="166" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="167" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
@@ -891,6 +929,180 @@
         <v>39</v>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" s="2">
+        <v>20.0</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E23" s="2">
+        <v>17.0</v>
+      </c>
+      <c r="G23" s="5">
+        <v>46357.0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2">
+        <v>21.0</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E24" s="2">
+        <v>14.0</v>
+      </c>
+      <c r="G24" s="5">
+        <v>46357.0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2">
+        <v>22.0</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E25" s="2">
+        <v>24.0</v>
+      </c>
+      <c r="G25" s="8">
+        <v>46044.0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2">
+        <v>23.0</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E26" s="2">
+        <v>17.0</v>
+      </c>
+      <c r="G26" s="9">
+        <v>46296.0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2">
+        <v>24.0</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E27" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="G27" s="5">
+        <v>46205.0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2">
+        <v>25.0</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E28" s="2">
+        <v>17.0</v>
+      </c>
+      <c r="G28" s="8">
+        <v>46054.0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2">
+        <v>26.0</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E29" s="2">
+        <v>17.0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2">
+        <v>27.0</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E30" s="2">
+        <v>43.0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2">
+        <v>28.0</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E31" s="2">
+        <v>27.0</v>
+      </c>
+      <c r="G31" s="8">
+        <v>46080.0</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/anime_library/anime_data.xlsx
+++ b/anime_library/anime_data.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="82">
   <si>
     <t>№</t>
   </si>
@@ -46,55 +46,150 @@
     <t>представник «Чорних биків»</t>
   </si>
   <si>
+    <t>Трошки горда і пихата, намагається триматися вище за інших, особливо приховуючи свої почуття до Асти. Через невміння контролювати магію в дитинстві зазнавала знущань від братів та сестри. Ноель володіє величезною магічною силою води, використовує атаки водяними кулями, захисний купол «Логово морського дракона», «Рев Морського дракона» та бойовий обладунок «Плаття Валькірії», який також має форму русалки для битв під водою.</t>
+  </si>
+  <si>
     <t>Ванесса</t>
   </si>
   <si>
+    <t>Висока молода жінка з рожевим хвилястим волоссям до середини спини та фіолетовими очима, член загону «Чорний бик». Вона полюбляє алкоголь і відвертий одяг, часто ходить базою лише в нижній білизні та накидці загону. Ванесса має невимушені манери, любить красивих чоловіків і не соромиться привертати їхню увагу. Вона народилася у Відьминому Лісі та була улюбленицею Королеви Відьом, але втекла звідти разом із Ямі Сукехіро. Ванесса володіє магією нитей, а її найсильніша здібність - Червона Нитка Долі у вигляді рудої кішки на ім'я Руж, яка може змінювати долю й захищати союзників від будь-яких атак. Вона дуже віддана своєму загону та вважає його своєю справжньою родиною.</t>
+  </si>
+  <si>
     <t>Ямі</t>
   </si>
   <si>
+    <t>Високий мускулистий чоловік із чорним волоссям і бородою, нащадок клану Ямі з Країни Сонця. У дитинстві він потрапив до Королівства Конюшини, де згодом став першим капітаном загону «Чорний бик».
+Ямі хоч грубий, лінивий і нетерплячий, проте щиро піклується про свій загін, ставлячись до нього як до родини. Він володіє рідкісною магією темряви, є майстром фехтування на катанах та вміло використовує кі й зону мани.
+Його улюблена фраза: «Переверш свої межі!»</t>
+  </si>
+  <si>
     <t>Фінрал</t>
   </si>
   <si>
+    <t>Дворянин з Дому Вод, молодший лицар-маг 1-го класу загону «Чорний бик». Він стрункий юнак із світло-каштановим волоссям та «обвислими» очима. Фінрал дуже любить фліртувати з дівчатами та часто заграє з ними, але після битви з ельфами вирішує стати гідним своєї нареченої Фінесси та відмовитися від залицянь до інших. Він боягузкуватий, але легко стає хоробрим заради жінок або підкупу. Фінрал володіє рідкісною просторовою магією - може відкривати портали, але лише туди, де він уже був або що бачив. Його основні заклинання: «Врата Падшого Янгола» та «Змах Падшого Янгола». Після навчання в Королівстві Серця він опанував Метод Мани для пришвидшення заклинань. Фінрал мріє не стати найсильнішим сам, а зробити «Чорного бика» найсильнішим загоном.</t>
+  </si>
+  <si>
     <t>Чармі</t>
   </si>
   <si>
+    <t>Мініатюрна дівчина з чорним волоссям до плечей і зеленими очима, гібрид людини та дворфа, а також молодший лицар-маг 1-го класу загону «Чорний бик». Обожнює їжу й майже постійно думає про неї. Зазвичай вона мила та безтурботна, але стає холодною й безжальною, якщо хтось намагається забрати або зіпсувати її їжу. Попри це, вона дуже щедра та із задоволенням ділиться стравами з друзями.
+Вона володіє двома видами магії. Перша - магія бавовни, за допомогою якої Чармі створює овечок-кухарів, платформи та магічні пастки чи обмеження. Друга - магія їжі, що дозволяє поглинати інші види магії. Під час її використання Чармі перетворюється на високу дорослу жінку з розпущеним волоссям.
+Чармі має величезний запас мани, який значно зростає через лють або коли хтось зазіхає на її їжу. Вона закохана в Юно і постійно сперечається через нього з духом Сильфіда. Її улюблена фраза: «Мені байдуже, хто це - ніхто не чіпатиме мою їжу!».</t>
+  </si>
+  <si>
     <t>Неро</t>
   </si>
   <si>
+    <t>Секре Сваллотейл - невисока струнка дівчина з чорним волоссям каре та двома чорними ріжками на голові, дворянка й колишня служниця принца Люм’єр Сільвамілліон Кловер - першого Короля Магів.
+Щоб урятувати Люм’єра, Секре використала заборонну магію й запечатала його в статую, але через це сама перетворилася на анти-птицю на ім’я Неро. Через 500 років вона зустріла Аста, прив’язалася до нього та після повернення людської форми приєдналася до загону «Чорний бик».
+Секре зазвичай апатична, спокійна й незворушна. Вона має звичку клювати Асту в голову, коли той поводиться нерозумно або робить щось не так, але водночас дуже віддана йому та завжди підтримує його. Її магія - магія запечатування, яка дозволяє запечатувати людей, предмети й навіть рани. Також Секре володіє магією зцілення. Вона має величезний запас мани, здатна відчувати ману на великій відстані, а після тренувань у Королівстві Серця опанувала Метод Мани. Її улюблена фраза: «Люди, на яких ти дивишся згори, яких змушуєш страждати.. ці люди сьогодні переможуть тебе!».</t>
+  </si>
+  <si>
     <t>Грей</t>
   </si>
   <si>
-    <t>Зоро</t>
+    <t>Молода дівчина середнього зросту з коротким світло-блакитним волоссям, простолюдинка та молодший лицар-маг 3-го класу загону «Чорний бик».
+Грей надзвичайно сором’язлива й невпевнена у своїй справжній зовнішності, тому часто використовує магію, щоб перетворюватися на інших людей - найчастіше на високого чоловіка з чорним волоссям. Попри важке дитинство та знущання з боку мачухи й зведених сестер, вона залишилася доброю та щирою, хоча й дещо наївною.
+Вона володіє магією трансформації, яка дозволяє змінювати власну зовнішність, а також магією перетворення - здатністю змінювати одну речовину на іншу. Грей може перетворювати камінь на м’ясо, щупальця на рослини, гель на кристали й навіть зашивати рани. Через здатність впливати на немагічні речовини її вважають магом Таємної Стадії.
+Грей дуже віддана загону «Чорний бик», а особливо Гош Адлай, який колись урятував її від грабіжників.
+Її улюблена фраза: «Краще смерть, ніж нездатність трансформуватися назад!».</t>
+  </si>
+  <si>
+    <t>Зора</t>
+  </si>
+  <si>
+    <t>Молодший лицар-маг 1-го класу загонів «Чорний бик» і «Королівські лицарі», син Зара Ідеаре - першого простолюдина, який став лицарем-магом.
+Його найпомітніші риси - чорні шкіряні ремінці, що закривають нижню частину обличчя, скуйовджене багрове волосся та бліда шкіра. Зора зневажливо ставиться майже до всіх: дворян, лицарів-магіків, Короля Магів і навіть самого себе. Він полюбляє насмішки, провокації та часто кидає в людей «райдужних смердючих жуків».
+Через трагічну смерть батька, якого вбили власні товариші по загону лише за те, що він був простолюдином, Зора зненавидів корумпованих лицарів-магів і почав полювати на них. Попри грубу поведінку, він має сильне почуття справедливості та поважає тих, хто чесно бореться за інших.
+Він володіє магією попелу та магією пасток. Він створює складні рунні пастки, здатні паралізувати ворогів, поглинати магію та відбивати закляття назад із подвоєною силою. Для простолюдина Зора має величезний запас мани, а також вирізняється високим інтелектом, витривалістю та швидкістю. Його улюблена фраза: «Виродки на кшталт вас - не лицарі-маги!».</t>
   </si>
   <si>
     <t>Гордон</t>
   </si>
   <si>
+    <t xml:space="preserve">Стрункий молодий чоловік із блідою шкірою, чорним волоссям, червоними очима з великими темними колами, чорною помадою та лаком на нігтях, простолюдин і молодший лицар-маг 1-го класу загону «Чорний бик».
+Гордон постійно тихо щось бурмоче, через що його майже ніхто не може зрозуміти. Його моторошна зовнішність часто лякає людей, хоча насправді він дуже добрий, чуйний і щиро мріє подружитися з усіма членами свого загону.
+Він народився в родині Аґріппа, відомій використанням магії проклять, але залишив сім’ю через самотність і відсутність друзів. Гордон володіє магією отрути, за допомогою якої створює отруйних барсуків та токсичні хмари, а також магією проклять, що дозволяє посилювати ефекти заклинань. Після навчання у батька він навчився перетворювати отруту на лікувальні засоби, які можуть підсилювати союзників.
+Його улюблена фраза: «Еххх! Я хочу швидше з усіма потоваришувати».
+</t>
+  </si>
+  <si>
     <t>Магна</t>
   </si>
   <si>
+    <t>Молодий чоловік худорлявої статури з двоколірним волоссям - світлим на маківці та чорним з боків - і чорним ірокезом. Він має прямий шрам на лівому боці чола, носить чорні сонцезахисні окуляри та є простолюдином із села Раяка і молодшим лицарем-магом 5-го класу загону «Чорний бик».
+Маґна поводиться як типовий «крутий хлопець»: він запальний, прямолінійний і часто кидається в бій без вагань. Водночас він дуже відданий своєму капітанові Ямі Сукехіро і завжди готовий захищати товаришів по загону.
+Його основна сила - магія вогню, за допомогою якої Маґна створює вогняні кулі, картеч і тюремні кулі. Також він використовує магію обмеження у вигляді вогняних кайданів, магію створення для формування бейсбольної бити та кастетів, а ще магію посилення.
+Після виснажливих тренувань із Зора Ідеаре він створив унікальне закляття - «Духовний ланцюг смертельної битви», яке зрівнює магічну силу двох супротивників. Саме завдяки цій техніці Маґна зміг перемогти Данте Зоґратіс.
+Його улюблена фраза: «Розпастися? Як же, чекай, дурню! Якби я здався, то.. не посмів би показатися йому на очі як сенпай!».</t>
+  </si>
+  <si>
     <t>Лакк</t>
   </si>
   <si>
+    <t>Юнак невисокого зросту зі світлим скуйовдженим волоссям середньої довжини та блакитними очима, простолюдин і молодший лицар-маг 5-го класу загонів «Чорний бик» та «Королівські лицарі».
+Лак має майже соціопатичний характер: він постійно усміхається й отримує справжнє задоволення від битв із сильними супротивниками. Через свою одержимість боями він отримав прізвисько «Усміхнений маніяк битв». Лак обожнює битися та часто дратує своїх товаришів по загону своєю надмірною жагою до сутичок.
+Він володіє магією блискавки, створюючи потужні техніки на кшталт «Грозового Хогьоку», «Демона грому» та «Бойового чудовиська блискавки». Також Лак використовує магію створення для формування черевиків і рукавиць бога грому. Однією з його найсильніших особливостей є надзвичайно розвинений сенсор мани, що дозволяє відчувати магію на величезних відстанях.Після одержимості ельфом Луфулу Лак зберіг частину його сили. А після тренувань у Королівстві Серця він опанував Метод Мани та досяг рівня мага Першого рівня.
+Його улюблена фраза: «Поки я можу битися з крутими хлопцями, я в порядку.»</t>
+  </si>
+  <si>
     <t>Гош</t>
   </si>
   <si>
+    <t>Високий стрункий юнак зі світлим волоссям, що закриває ліве око (замість нього в нього вставлено маленьке магічне дзеркальце), колишній дворянин і молодший лицар-маг 1-го класу загону «Чорний бик».
+Гошу має доволі недружелюбний, егоїстичний характер і одержимо любить свою молодшу сестру Марі Адлаї. Він постійно носить її фотографію, прикрашає одяг шпильками з її ініціалами, а при думках про неї часто надмірно емоційно реагує.
+Його особистість сформувалася після трагедії: батьків Гошу вбили «друзі»-дворяни, які підробили заповіт і вигнали його разом із Марі на вулицю. Згодом він почав поступово більше довіряти своїм товаришам по загону «Чорний бик».
+Гошу володіє магією дзеркал, яка дозволяє відбивати світло, створювати лазерні промені, дзеркальних клонів, віддзеркалювати закляття, множити союзників і змінювати позиції цілей. Як дворянин він має великий запас мани, а після одержимості ельфом Дрова зберіг частину його сили.
+Його улюблена фраза: «Тільки ти мені й потрібна, Марі! Хай усі зникнуть, мені байдуже!».</t>
+  </si>
+  <si>
     <t>27.06..2026</t>
   </si>
   <si>
     <t>Нахт</t>
   </si>
   <si>
+    <t>Колишній дворянин, віце-капітан загону «Чорний бик» і господар чотирьох діяволів середнього рангу - Гімодело, Слотос, Плюмеде та Вальґнер.
+Він має довге чорне волосся, зібране в хвіст, блакитні очі, шрам на лівому зап’ясті та носить намисто з чотирма реліквіями, що пов’язані з його діяволами.
+Нахт - прагматичний, логічний і надзвичайно самокритичний. Він глибоко ненавидить безпричинне зло й переконаний, що добрі вчинки не здатні повністю виправити минулі помилки. Така позиція сформувалася через загибель його брата-близнюка Морґен Фауст, якого випадково вбив викликаний ним же диявол.
+У минулому Нахт був шпигуном у Піковому Королівстві, а згодом став наставником Аста, готуючи його до майбутніх битв і вторгнення.
+Його магія - магія тіней, яка дозволяє переміщатися крізь тіні, обездвижувати ворогів, хапати їх, створювати тіньові коридори та в’язниці. Також він використовує чотири режими об’єднання з дияволами: Каніс (пес), Еквус (кінь), Феліс (кіт) і Галус (півень), кожен із яких дає унікальні бойові можливості.
+Його улюблена фраза: «Безпричинне зло я ненавиджу найбільше. Навіть якщо його простять боги й дияволи, я - ніколи».</t>
+  </si>
+  <si>
     <t>Генрі</t>
   </si>
   <si>
+    <t xml:space="preserve">Блідий юнак із довгим скуйовдженим білим волоссям, у якому живуть птахи. Він дворянин і молодший лицар-маг 5-го класу загону «Чорний бик».
+Генрі надзвичайно добрий і жертовний, дуже цінує своїх товаришів, але говорить повільно й м’яко, через що часто здається відстороненим. Через прокляття він постійно й пасивно поглинає магічну силу оточуючих, тому довгий час був прикутий до ліжка у відлюдному будинку.
+Його врятував капітан Ямі Сукехіро, запросивши до загону «Чорний бик». Відтоді Генрі живиться запасами мани своїх товаришів і став важливою частиною команди.
+Він володіє магією перебудови, що дозволяє змінювати форму та розташування кімнат у чарівному будинку - базі «Чорного бика». Також може перетворювати будинок на гігантського або мініатюрного бика, використовувати техніки на кшталт «Мана-Штопор» і «Реактивний удар маною».
+Його улюблена фраза: «Якщо ви спробуєте завдати шкоди моїм друзям, я вас не пробачу».
+</t>
+  </si>
+  <si>
     <t>Шарлотта</t>
   </si>
   <si>
+    <t>представник «Блакитна троянда»</t>
+  </si>
+  <si>
+    <t>Висока дворянка, капітан загону «Блакитна троянда», з довгим світлим волоссям, зібраним у пучок, і невеликою косою з лівого боку обличчя. Вона має блакитні очі та зазвичай носить обладунки й шолом, попри свою відому красу.
+Шарлотта тримається холодно, стримано й суворо. Вона повністю присвячує себе службі королівству та не цікавиться світським життям, особливо розмовами про шлюб чи пошук чоловіка. Водночас вона таємно закохана в Ямі Сукехіро, який колись урятував її від прокляття, але через свою гордість і характер не може цього відкрито показати та поводиться з ним доволі різко.
+Вона володіє магією шипшини, що дозволяє створювати сині троянди, шипи, лози та списоподібні конструкції. Після тренувань у Королівстві Серця Шарлотта опанувала Метод Мани та Істинну магію шипшини, яка проявляється у вигляді червоних троянд без прокляття.
+Її улюблена фраза: «Поле бою - мій єдиний супутник».</t>
+  </si>
+  <si>
+    <t>Мімоза</t>
+  </si>
+  <si>
     <t>представник «Золотий світанок»</t>
   </si>
   <si>
-    <t>Мімоза</t>
+    <t>Молода дворянка з королівського дому Вермілліон, середній лицар-маг 5-го класу загонів «Золотий світанок» та «Королівські лицарі». Вона має довге хвилясте руде волосся, жовті очі та маленькі червоні сережки, а також вирізняється м’якою, привітною зовнішністю.
+Мімоза добра, ввічлива й завжди усміхнена, але водночас напрочуд прямолінійна, що інколи межує з різкістю. На відміну від багатьох дворян, вона не виявляє зверхності й оцінює людей за їхні вчинки та характер. Вона глибоко поважає свою кузину Ноель Сільва і має романтичні почуття до Аста, який колись урятував її від Марс.
+У дитинстві Мімоза була досить незграбною, часто спотикалася навіть на рівному місці. Вона володіє магією рослин, яка дозволяє створювати квіти, трави, бойові конструкції та квітку-путівник, а також потужною магією зцілення, здатною рятувати навіть тих, хто перебуває на межі смерті. Крім того, вона вміє відчувати ману оточення. Після тренувань у Королівстві Серця Мімоза опанувала Метод Мани та вдосконалену магію, значно підвищивши свої бойові та лікувальні здібності.
+Її улюблена фраза: «Мені не потрібна причина, щоб врятувати когось на межі смерті! Мені байдуже, навіть якщо це ворог чи хтось іншої раси!».</t>
   </si>
   <si>
     <t>Дитя погоди</t>
@@ -106,31 +201,52 @@
     <t>головний герой</t>
   </si>
   <si>
+    <t>Темноволосий, трохи неохайний підліток, який утік з дому до Токіо, намагаючись вирватися з задушливої рутини та знайти своє місце у світі.
+У великому місті Ходака почувається чужим, розгубленим і наївним, але всередині нього є сильний внутрішній стрижень. Він упертий, чутливий і рішучий, здатний сміливо протистояти жорстокості світу та власним страхам, поступово дорослішаючи через пережиті випробування.
+Зустріч із Хіна Амано стає для нього поворотним моментом: саме вона відкриває в ньому приховану рішучість і готовність боротися за те, що для нього справді важливе.
+Із замкнутого хлопця, який не знає, кому довіряти, Ходака перетворюється на людину, готову йти до кінця, навіть якщо це суперечить правилам і суспільним очікуванням.</t>
+  </si>
+  <si>
     <t>Хіна</t>
   </si>
   <si>
     <t>головна героїня</t>
   </si>
   <si>
+    <t>Струнка дівчина з темним волоссям і добрим поглядом, відома як «сонячна дівчина», яка щиро любить своїх близьких.
+Вона оптимістична, турботлива та наполеглива - справжнє втілення променя світла, що пробивається крізь нескінченні дощі. Попри юний вік, Хіна вже взяла на себе багато дорослих обов’язків і намагається триматися навіть тоді, коли обставини підштовхують до відчаю. Її усмішка - це не наївність, а свідомий вибір залишатися сильною.
+Хіна завжди шукає надію навіть у найтемніші моменти, коли інші її вже не бачать. Разом із даром, що пов’язаний із керуванням погодою, вона несе й внутрішній тягар - відчуття відповідальності за те, як її здібності впливають на життя інших, через що вона стає вразливою. Вона боїться не за себе, а за тих, кого любить.
+Її зв’язок із Ходака Морісіма - це зустріч двох самотностей, що поступово перетворюється на союз двох людей, які готові боротися за одне одного і за власний вибір.</t>
+  </si>
+  <si>
     <t>Нацумі</t>
   </si>
   <si>
     <t>Другорядний персонаж</t>
   </si>
   <si>
-    <t>племінниця Кейсуке</t>
+    <t>Стильна, яскрава й енергійна дівчина, весела, хоробра та захоплена життям, але водночас трохи хаотична. Вона з’являється в історії як справжній «вибух» енергії та харизми, що ніби ураган змінює атмосферу навколо себе.
+Нацумі працює разом із Кейсуке Суґа і водночас стає для Ходака Морісіма своєрідною старшою сестрою - з піддражнюванням, підтримкою та легким хаосом, який вона приносить у його життя.
+Вона не боїться нових ситуацій і часто діє імпульсивно, повністю занурюючись у момент. Її енергія, гумор і безпосередність роблять її джерелом тепла й легкості в сюжеті. Водночас за цією легкістю стоїть власна історія - пошук себе, кар’єри та свого місця у світі.
+Нацумі уособлює молодість і прагнення досягти чогось великого, навіть якщо поки що незрозуміло, чого саме. Вона додає історії відчуття руху, оптимізму й віри в можливості життя.</t>
   </si>
   <si>
     <t>Нагі</t>
   </si>
   <si>
-    <t>молодший брат гг</t>
+    <t>Акуратний, привабливий школяр, комунікабельний, упевнений у собі та добре розуміється на стосунках. Він є молодшим братом Хіна Амано і водночас важливою емоційною опорою для неї.
+Наґі має напрочуд зрілий характер для свого віку: він легкий у спілкуванні, швидко знаходить спільну мову з людьми та навіть дає поради щодо стосунків, через що часто поводиться так, ніби значно старший - майже як дорослий. Його впевненість і природна харизма роблять його привабливим як для однолітків, так і для дорослих.
+Попри легкість характеру, Наґі дуже турботливий і уважний до сестри - він тонко відчуває її настрій і завжди намагається підтримати її, коли це потрібно. Його дружба з Ходака Морісіма - це стосунки двох хлопців із близьким внутрішнім відчуттям світу, які швидко знаходять спільну мову.
+Наґі додає історії легкість, гумор і теплі, життєві моменти, водночас показуючи, що навіть у дитячому віці можна мати глибоке розуміння людей і стосунків.</t>
   </si>
   <si>
     <t>Кейсуке</t>
   </si>
   <si>
-    <t>орендар</t>
+    <t>Досить втомлений чоловік із недбалим стилем, який на перший погляд здається цинічним і різким, але насправді є уважним і добрим.
+Він стає наставником Ходака Морісіма і підтримує його в адаптації до життя в Токіо, допомагаючи знайти роботу, житло та базове розуміння міського життя. Попри зовнішню грубість, Кейсуке бачить у Ходаці не проблему, а людину, яка потребує підтримки та напрямку.
+Його власне життя далеке від ідеального: він стикається з побутовими труднощами, робочими проблемами та складними сімейними обставинами. Проте крізь цинізм і втому постійно проявляється його внутрішня турбота про інших.
+Кейсуке уособлює реальність дорослого світу - той період, коли ілюзії зникають, і доводиться жити з відповідальністю, проблемами та складними виборами, не втрачаючи людяності.</t>
   </si>
   <si>
     <t>Твоє ім'я</t>
@@ -139,28 +255,91 @@
     <t>Міцуха</t>
   </si>
   <si>
+    <t>головна героїня, яка мріє вирватися з тихого життя в селі Ітоморі та переїхати до Токіо. Вона приваблива дівчина з чорним волоссям, зібраним у характерні оригінальні кіски, та добрими карими очима.
+Міцуха добра, чутлива та ініціативна. Вона прагне внести порядок у своє оточення й ставиться до людей відкрито та щиро. Її жага до змін і пригод особливо проявляється через містичний зв’язок із Такі Татібана, юнаком із Токіо, з яким вона починає обмінюватися тілами.
+Життя в селі здається їй обмеженим, тому вона прагне міського ритму та нових можливостей, але водночас пишається своєю роллю служниці в місцевому храмі й шанує традиції та історію рідного міста.
+Її стосунки з Такі стають центральною частиною історії: через обмін тілами вони поступово пізнають одне одного, навчаються розуміти різні світи та підтримують зв’язок, попри відстань і обставини, що їх розділяють.</t>
+  </si>
+  <si>
     <t>Такі</t>
   </si>
   <si>
+    <t>Головний герой, який живе в Токіо. Працьовитий і відповідальний школяр, він підробляє офіціантом в італійському ресторані та мріє про спокійне життя подалі від міської метушні. Герой обдарований фотографічною пам’яттю та художнім талантом, уміє точно передавати найменші деталі. Вибуховий характер та імпульсивність часто призводять до синців і подряпин, але саме ця енергія допомагає йому долати перешкоди. Особливу роль у його житті відіграє таємничий зв’язок із Міцухою Міямідзу, з якою вони періодично чарівним чином обмінюються тілами. Ця взаємодія не лише допомагає героям впоратися з життєвими проблемами, але й кардинально змінює їхні долі.</t>
+  </si>
+  <si>
     <t>Мікі</t>
   </si>
   <si>
+    <t>Другорядна, але яскрава персонажка аніме «Твоє ім’я». Вона працює офіціанткою в італійському ресторані та підтримує головного героя Такі Татібана, допомагаючи йому налагодити зв’язок із Міцуха Міямідзу.
+Мікі приваблива, добра й привітна, її манери та зовнішність викликають симпатію як у колег, так і у відвідувачів ресторану. Вона виступає як спокійна, доросла опора в історії, додаючи їй тепла й реалістичності.
+У фіналі історії показано, що вона вийшла заміж. Згідно з уточненням автора Макото Сінкай, її чоловіком став Цукаса Фудзі - близький друг Такі.</t>
+  </si>
+  <si>
     <t>Цукаса</t>
   </si>
   <si>
+    <t>Юнак із дещо суворим, але справедливим характером і найкращий друг Такі Татібана. Він завжди підтримує Такі, виявляючи турботу та уважність, дає своєчасні поради та допомагає йому в складних ситуаціях.
+Попри зовнішню стриманість, Цукаса надійний і чуйний друг, на якого можна покластися.
+Наприкінці історії він одружується з Мікі Окудера і згодом займається флористикою, знаходячи для себе спокійний і творчий життєвий шлях.</t>
+  </si>
+  <si>
     <t>Йоцуха</t>
   </si>
   <si>
+    <t>молодша сестра головної героїні Міцуха Міямідзу. Ще в дитинстві вона втратила матір, а батько залишив сім’ю, тому виховання дівчаток взяла на себе бабуся.
+Йоцуха - життєрадісна та працьовита дівчинка, яка активно бере участь у ритуальних заходах храму. Вона допомагає виготовляти саке та плести традиційні шнури, серйозно ставиться до своїх обов’язків і охоче підтримує старших.
+У 2013 році вона ледь не загинула під час катастрофи, спричиненої падінням комети Тіамат, але була врятована завдяки діям Міцухи. Через дев’ять років Йоцуха виросла й вступила до середньої школи, зберігши свій оптимізм, відповідальність і життєрадісність.</t>
+  </si>
+  <si>
     <t>Саяка</t>
   </si>
   <si>
+    <t>подруга та однокласниця Міцуха Міямідзу. Вона має каштанове волосся, заплетене в косички, і родимку під лівим оком. Саяка вирізняється спокійним і добрим характером.
+Вона поділяє мрії Міцухи про життя у великому місті та також хоче залишити невелике селище Ітоморі, щоб переїхати до Токіо. У школі Саяка є старанною ученицею та веде блог на шкільній радіостанції, а також завжди підтримує своїх подруг.
+У початковій часовій лінії Саяка гине під час катастрофи, спричиненої падінням комети Тіамат. Однак завдяки діям Міцухи та Такі Татібана трагедії вдається запобігти.
+У зміненому майбутньому Саяка виживає, згодом переїжджає до Токіо й виходить заміж за Кацухіко Тесіґавару.</t>
+  </si>
+  <si>
     <t>Шінта</t>
   </si>
   <si>
+    <t>друг Такі Татібана, високий і кремезний юнак із м’якими рисами обличчя та світло-каштановим волоссям.
+Він має оптимістичний і доброзичливий характер, завжди готовий підтримати друзів у складну хвилину. Шінта вирізняється розважливістю та впевненістю, часто стаючи емоційною опорою для оточуючих.
+У шкільні роки він носить класичну японську шкільну форму, а в дорослому житті змінює її на стильний діловий костюм, що підкреслює його зрілість і професійність.</t>
+  </si>
+  <si>
     <t>Тосікі</t>
   </si>
   <si>
+    <t>другорядний, але важливий персонаж аніме «Твоє ім’я», батько Міцуха Міямідзу та Ецуха Міямідзу. Після смерті дружини він обійняв посаду мера невеликого містечка Ітоморі.
+Його рішення та кар’єра погіршили стосунки з бабусею дівчаток, яка звинувачувала його у втраті традицій і недостатній увазі до виховання онучок.
+Тосікі - сумлінний, відповідальний, але дуже зайнятий чиновник, який часто змушений ставити роботу вище за особисте життя. Спочатку він скептично ставився до попереджень Міцухи про майбутню катастрофу, однак у критичний момент усе ж прислухався до доньки й вжив рішучих заходів, що допомогло врятувати мешканців Ітоморі від падіння метеорита Тіамат.
+Попри зайнятість, Тосікі щиро піклується про своїх доньок і намагається забезпечити їхню безпеку та майбутнє.</t>
+  </si>
+  <si>
     <t>Юкарі</t>
+  </si>
+  <si>
+    <t>другорядна персонажка у фільмі «Твоє ім’я», яка також відома як викладачка японської мови з аніме Сад витончених слів.
+Вона молода, приваблива, добра й емоційно вразлива. У своїй основній історії Юкарі працює в середній школі, де навчає головного героя Такао Акідзукі. Через чутки та плітки, що виникли після ситуації з учнем, її кар’єра опиняється під загрозою, що спричиняє внутрішню кризу та період депресії.
+Зустріч із Такао стає для неї важливим емоційним переломним моментом, допомагаючи їй поступово віднайти опору та сенс у житті.
+Камео Юкарі у «Твоє ім’я» слугує своєрідним зв’язком між різними роботами режисера Макото Сінкай, підкреслюючи умовну єдність його анімаційних світів і персонажів.</t>
+  </si>
+  <si>
+    <t>Волейбол</t>
+  </si>
+  <si>
+    <t>Хіната</t>
+  </si>
+  <si>
+    <t>Головний герой</t>
+  </si>
+  <si>
+    <t>головний герой аніме та манґи «Волейбол!». Він почав грати у волейбол після того, як побачив легендарного гравця «Маленького гіганта» зі школи Карасуно, який, попри низький зріст, перемагав значно вищих суперників.
+Хіната має руде кучеряве волосся, карі очі та зріст 162,8 см (до кінця першого року виріс до 164,2 см). Він життєрадісний, енергійний, простий у спілкуванні, але дуже чутливий до емоцій інших людей. Попри природну боязкість перед високими суперниками, Хіната надзвичайно наполегливий і ніколи не здається на майданчику.
+Його ключові фізичні переваги - витривалість, швидкість і вибухова стрибучість (вертикальний стрибок близько 1,23 м). Разом із Кагеяма Тобіо він створив фірмову комбінацію - «швидкий удар мінус-темпу», яка стала однією з найнебезпечніших атак у грі.
+Хінату часто називають «абсолютною приманкою», адже він вміє притягувати увагу блокуючих і відкривати простір для команди. Після школи він два роки тренувався в Бразилії у пляжному волейболі, грав за команду MSBY Black Jackals та за збірну Japan men's national volleyball team.
+Його головна мрія - побачити «вид згори», краєвид, який відкривається лише найвищим і найсильнішим гравцям.</t>
   </si>
 </sst>
 </file>
@@ -477,6 +656,7 @@
   <cols>
     <col customWidth="1" min="1" max="2" width="17.38"/>
     <col customWidth="1" min="4" max="4" width="28.75"/>
+    <col customWidth="1" min="6" max="6" width="34.75"/>
     <col customWidth="1" min="7" max="7" width="15.5"/>
   </cols>
   <sheetData>
@@ -522,6 +702,9 @@
       <c r="E2" s="2">
         <v>15.0</v>
       </c>
+      <c r="F2" s="3" t="s">
+        <v>11</v>
+      </c>
       <c r="G2" s="4">
         <v>46341.0</v>
       </c>
@@ -534,13 +717,16 @@
         <v>8</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>10</v>
       </c>
       <c r="E3" s="2">
         <v>24.0</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="G3" s="5">
         <v>46158.0</v>
@@ -554,13 +740,16 @@
         <v>8</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>10</v>
       </c>
       <c r="E4" s="2">
         <v>28.0</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="G4" s="5">
         <v>46282.0</v>
@@ -574,13 +763,16 @@
         <v>8</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>10</v>
       </c>
       <c r="E5" s="2">
         <v>21.0</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="G5" s="5">
         <v>46059.0</v>
@@ -594,13 +786,16 @@
         <v>8</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>10</v>
       </c>
       <c r="E6" s="2">
         <v>19.0</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="G6" s="5">
         <v>46176.0</v>
@@ -614,13 +809,16 @@
         <v>8</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>10</v>
       </c>
       <c r="E7" s="2">
         <v>17.0</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="G7" s="5">
         <v>46191.0</v>
@@ -634,13 +832,16 @@
         <v>8</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>10</v>
       </c>
       <c r="E8" s="2">
         <v>24.0</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>23</v>
       </c>
       <c r="G8" s="5">
         <v>46073.0</v>
@@ -654,13 +855,16 @@
         <v>8</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>10</v>
       </c>
       <c r="E9" s="2">
         <v>25.0</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="G9" s="4">
         <v>46375.0</v>
@@ -674,13 +878,16 @@
         <v>8</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>10</v>
       </c>
       <c r="E10" s="2">
         <v>26.0</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="G10" s="5">
         <v>46035.0</v>
@@ -694,13 +901,16 @@
         <v>8</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>10</v>
       </c>
       <c r="E11" s="2">
         <v>18.0</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>29</v>
       </c>
       <c r="G11" s="5">
         <v>46119.0</v>
@@ -714,13 +924,16 @@
         <v>8</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>10</v>
       </c>
       <c r="E12" s="2">
         <v>18.0</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="G12" s="4">
         <v>46306.0</v>
@@ -734,7 +947,7 @@
         <v>8</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>10</v>
@@ -742,8 +955,11 @@
       <c r="E13" s="2">
         <v>19.0</v>
       </c>
+      <c r="F13" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="G13" s="2" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
@@ -754,13 +970,16 @@
         <v>8</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>10</v>
       </c>
       <c r="E14" s="2">
         <v>29.0</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="G14" s="5">
         <v>46142.0</v>
@@ -774,13 +993,16 @@
         <v>8</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>10</v>
       </c>
       <c r="E15" s="2">
         <v>26.0</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="G15" s="5">
         <v>46065.0</v>
@@ -794,13 +1016,16 @@
         <v>8</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="E16" s="2">
         <v>27.0</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="G16" s="5">
         <v>46283.0</v>
@@ -814,13 +1039,16 @@
         <v>8</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E17" s="2">
         <v>15.0</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="G17" s="5">
         <v>46260.0</v>
@@ -831,16 +1059,19 @@
         <v>15.0</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="E18" s="2">
         <v>16.0</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="G18" s="5">
         <v>46140.0</v>
@@ -851,16 +1082,19 @@
         <v>16.0</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="E19" s="2">
         <v>15.0</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>51</v>
       </c>
       <c r="G19" s="5">
         <v>46256.0</v>
@@ -871,19 +1105,19 @@
         <v>17.0</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="E20" s="2">
         <v>21.0</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
     </row>
     <row r="21">
@@ -891,19 +1125,19 @@
         <v>18.0</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="E21" s="2">
         <v>10.0</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="G21" s="5">
         <v>46085.0</v>
@@ -914,19 +1148,19 @@
         <v>19.0</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="E22" s="2">
         <v>30.0</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
     </row>
     <row r="23">
@@ -934,16 +1168,19 @@
         <v>20.0</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="E23" s="2">
         <v>17.0</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>61</v>
       </c>
       <c r="G23" s="5">
         <v>46357.0</v>
@@ -954,16 +1191,19 @@
         <v>21.0</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="E24" s="2">
         <v>14.0</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>63</v>
       </c>
       <c r="G24" s="5">
         <v>46357.0</v>
@@ -974,16 +1214,19 @@
         <v>22.0</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="E25" s="2">
         <v>24.0</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>65</v>
       </c>
       <c r="G25" s="8">
         <v>46044.0</v>
@@ -994,16 +1237,19 @@
         <v>23.0</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="E26" s="2">
         <v>17.0</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>67</v>
       </c>
       <c r="G26" s="9">
         <v>46296.0</v>
@@ -1014,16 +1260,19 @@
         <v>24.0</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="E27" s="2">
         <v>9.0</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>69</v>
       </c>
       <c r="G27" s="5">
         <v>46205.0</v>
@@ -1034,16 +1283,19 @@
         <v>25.0</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="E28" s="2">
         <v>17.0</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>71</v>
       </c>
       <c r="G28" s="8">
         <v>46054.0</v>
@@ -1054,16 +1306,19 @@
         <v>26.0</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>47</v>
+        <v>72</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="E29" s="2">
         <v>17.0</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="30">
@@ -1071,16 +1326,19 @@
         <v>27.0</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="E30" s="2">
         <v>43.0</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="31">
@@ -1088,19 +1346,45 @@
         <v>28.0</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="E31" s="2">
         <v>27.0</v>
       </c>
+      <c r="F31" s="2" t="s">
+        <v>77</v>
+      </c>
       <c r="G31" s="8">
         <v>46080.0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2">
+        <v>29.0</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E32" s="2">
+        <v>15.0</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="G32" s="8">
+        <v>46194.0</v>
       </c>
     </row>
   </sheetData>
